--- a/education_forms/040_global_education_partnership_endorsement_request--education_forms.xlsx
+++ b/education_forms/040_global_education_partnership_endorsement_request--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,39 +520,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>global_education_partnership_endorsement_request_form_1</t>
+          <t>organization_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Global Education Prophets</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>รผ</t>
-        </is>
-      </c>
+          <t>Organization Name</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>organization_name</t>
+          <t>organization_type</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Organization Name</t>
+          <t>Organization Type</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -565,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>organization_type</t>
+          <t>global_education_impact</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Organization Type</t>
+          <t>Global Education Impact</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -588,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>global_education_partnership_endorsement_request_form_4</t>
+          <t>organization_address</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Global Education Impact</t>
+          <t>Organization Address</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -616,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>global_education_partnership_endorsement_request_form_5</t>
+          <t>organization_phone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Global Education Impact 2</t>
+          <t>Organization Phone</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -639,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>global_education_partnership_endorsement_request_form_6</t>
+          <t>organization_email</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Global Education Impact 3</t>
+          <t>Organization Email</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -662,87 +658,87 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>global_education_partnership_endorsement_request_form_7</t>
+          <t>global_education_focus_areas</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Prophets</t>
+          <t>Global Education Focus Areas</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>global_education_partnership_endorsement_request_form_8</t>
+          <t>organizational_structure</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Global Education</t>
+          <t>Organization Structure</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>global_education_partnership_endorsement_request_form_9</t>
+          <t>num_partners</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Global Education</t>
+          <t>Number of Partners</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>organization_address</t>
+          <t>project_duration</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Organization Address</t>
+          <t>Project Duration</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -754,340 +750,179 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>organization_email</t>
+          <t>num_beneficiaries</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Organization Email</t>
+          <t>Number of Beneficiaries</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>organization_phone</t>
+          <t>start_date</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Organization Phone</t>
+          <t>Start Date</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>global_education_partnership_endorsement_request_form_13</t>
+          <t>communication_plan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Global Education</t>
+          <t>Communication Plan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>organization</t>
+          <t>budget</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Budget</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>global_education_partnership_endorsement_request_form_15</t>
+          <t>skills_expertise</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Global Education</t>
+          <t>Skills/Expertise</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>global_education_partnership_endorsement_request_form_16</t>
+          <t>monitoring_evaluation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Global Education</t>
+          <t>Monitoring &amp; Evaluation</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>global_education_partnership_endorsement_request_form_17</t>
+          <t>start_date_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Global Education</t>
+          <t>Start Date 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>global_education_partnership_endorsement_request_form_18</t>
+          <t>end_date</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Global Prophets</t>
+          <t>End Date</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>global_education_partnership_endorsement_request_form_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Global Education</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>global_education_partnership_endorsement_request_form_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Global Education</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>global_education_partnership_endorsement_request_form_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Global Education</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>global_education_partnership_endorsement_request_form_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Global Education</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>global_education_partnership_endorsement_request_form_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Global Education</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>global_education_partnership_endorsement_request_form_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Global Education</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>global_education_partnership_endorsement_request_form_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1102,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>non-profit</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Non-Profit</t>
         </is>
       </c>
     </row>
@@ -1152,248 +987,316 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>global_education_partnership_endorsement_request_form_7_choices</t>
+          <t>organization_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>public</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Public</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>global_education_partnership_endorsement_request_form_7_choices</t>
+          <t>organization_type_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>government</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Government</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>organization_address_choices</t>
+          <t>global_education_focus_areas_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>early_childhood_education</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Early Childhood Education</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>organization_address_choices</t>
+          <t>global_education_focus_areas_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>primary_education</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Primary Education</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>organization_choices</t>
+          <t>global_education_focus_areas_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>secondary_education</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Secondary Education</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>organization_choices</t>
+          <t>global_education_focus_areas_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>tertiary_education</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Tertiary Education</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>global_education_partnership_endorsement_request_form_17_choices</t>
+          <t>global_education_focus_areas_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>special_education</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Special Education</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>global_education_partnership_endorsement_request_form_17_choices</t>
+          <t>organizational_structure_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>clear</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Clear</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>global_education_partnership_endorsement_request_form_20_choices</t>
+          <t>organizational_structure_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Unclear</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>global_education_partnership_endorsement_request_form_20_choices</t>
+          <t>communication_plan_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>global_education_partnership_endorsement_request_form_23_choices</t>
+          <t>communication_plan_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>global_education_partnership_endorsement_request_form_23_choices</t>
+          <t>skills_expertise_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>research</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Research</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>global_education_partnership_endorsement_request_form_24_choices</t>
+          <t>skills_expertise_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>consulting</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Consulting</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>global_education_partnership_endorsement_request_form_24_choices</t>
+          <t>skills_expertise_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>teaching</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Teaching</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>skills_expertise_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>skills_expertise_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>monitoring_evaluation_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>monitoring_evaluation_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
